--- a/RangeSayacv2.xlsx
+++ b/RangeSayacv2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB891E90-0703-43A6-AAA3-9866D15A259E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7448A9-582F-44BB-BBDE-E101021585C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F6BF37BD-FBCE-455B-B84F-487EBCBBCEE9}"/>
   </bookViews>
